--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.98712236373061</v>
+        <v>7.960407384106224</v>
       </c>
       <c r="D2" t="n">
-        <v>37.84964569203186</v>
+        <v>6.150567424955178</v>
       </c>
       <c r="E2" t="n">
-        <v>9.216388824507082</v>
+        <v>1.497663183982401</v>
       </c>
       <c r="F2" t="n">
-        <v>3.456456925980198</v>
+        <v>0.5616742504717824</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55434471471644</v>
+        <v>4.965081016141422</v>
       </c>
       <c r="D3" t="n">
-        <v>30.93673184007147</v>
+        <v>5.027218924011613</v>
       </c>
       <c r="E3" t="n">
-        <v>9.216388824507082</v>
+        <v>1.497663183982401</v>
       </c>
       <c r="F3" t="n">
-        <v>3.456456925980198</v>
+        <v>0.5616742504717824</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
